--- a/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>臺灣冬季吹什麼季風？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>東北季風</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>梅雨</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>冷乾</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>臺灣夏季吹什麼季風？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>梅雨</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>滯留鋒面</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>西南季風</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>熱濕</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>春末夏初的連日降雨是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>梅雨</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>較熱濕</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>較冷乾</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>滯留鋒</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>夏秋帶來強風豪雨的是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>颱風</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>較冷乾</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>較熱濕</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>低壓</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>颱風是高氣壓還低氣壓？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>夏秋</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>颱風眼</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>低氣壓</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>強烈</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>梅雨是什麼鋒面造成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>滯留鋒面</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>停留</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>東北季風帶來的天氣？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>夏秋</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>較冷乾</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>颱風常發生在什麼季節？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>梅雨</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>夏秋</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>季節</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>臺灣冬天吹的季風是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>溫暖海洋水氣</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>東北季風</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>夏秋</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>冷乾</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>夏秋侵襲臺灣帶來豪雨的是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>颱風</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>較熱濕</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>低壓</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>西南季風帶來的天氣特性？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>較熱濕</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>較冷乾</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>夏季</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>颱風中心稱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>溫暖海洋水氣</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>颱風眼</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>低壓中心</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>梅雨滯留鋒為何連日降雨？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>強東北季風冷空氣南下氣溫驟降</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>留意預警備糧遠離危險區</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>鋒面停留少移動</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>滯留</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>冬季寒流與什麼季風有關？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>滯留鋒面</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>東北季風</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>颱風眼</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>冷空氣</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>颱風帶來的正面效益？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>補充水資源</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>梅雨</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>夏秋</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>水源</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>臺灣屬於什麼氣候區？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>西南季風</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>季風氣候區</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>季風</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>颱風的能量來自？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>溫暖海洋水氣</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>季節</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>颱風</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>海溫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>季風隨什麼轉換？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>較冷乾</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>季節</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>東北季風</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>轉向</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>臺灣夏天吹的季風是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>季風氣候區</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>低氣壓</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>西南季風</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>滯留鋒面</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>熱濕</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>颱風屬於高氣壓還低氣壓？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>低氣壓</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>季節</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>滯留鋒面</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>溫暖海洋水氣</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>強烈</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下3-3 臺灣的天氣　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明臺灣冬夏季風方向與性質差異？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>冬東北季風冷乾、夏西南季風熱濕</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>迎風面多雨背風面較乾</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>致災同時補充水庫</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鋒面停留少移動</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>季風</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>颱風為何帶來強風豪雨？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾、夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>留意預警備糧遠離危險區</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>致災同時補充水庫</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>強烈低壓旋轉挾帶大量水氣</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>低壓</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>梅雨對臺灣的利與弊？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>強東北季風冷空氣南下氣溫驟降</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>補水但久雨易致災</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>利弊</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>面對颱風應如何防災？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>致災同時補充水庫</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>留意預警備糧遠離危險區</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>帶來大量降雨補充水庫</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>防災</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何颱風既是災害也是水資源？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>強東北季風冷空氣南下氣溫驟降</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>迎風面多雨背風面較乾</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>補水但久雨易致災</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>致災同時補充水庫</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>雙面</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>分析寒流成因與影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>強東北季風冷空氣南下氣溫驟降</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>鋒面停留少移動</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾、夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>寒流</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>臺灣多山對降雨分布影響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>致災同時補充水庫</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>補水但久雨易致災</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾、夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>迎風面多雨背風面較乾</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>地形雨</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>季風氣候如何塑造臺灣四季天氣？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>補水但久雨易致災</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>季風轉換帶來乾濕冷熱變化</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>鋒面停留少移動</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>說明臺灣冬夏季風的差異？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>季風轉換帶來乾濕冷熱變化</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾、夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>強東北季風冷空氣南下氣溫驟降</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>冬東北季風冷乾夏西南季風熱濕</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>季風</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何颱風也是重要水資源？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>留意預警備糧遠離危險區</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>帶來大量降雨補充水庫</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>冬東北季風冷乾夏西南季風熱濕</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>雙面</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>冷乾</t>
+          <t>冷乾：臺灣冬天主要吹從大陸方向來的東北季風，帶來比較寒冷乾燥的天氣</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>熱濕</t>
+          <t>熱濕：臺灣夏天主要吹從海洋方向來的西南季風，帶來比較炎熱潮濕的天氣</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>滯留鋒</t>
+          <t>滯留鋒：春天快結束、夏天剛開始時常出現連續多日下雨的現象，就是梅雨</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>低壓</t>
+          <t>低壓：夏秋兩季常出現的颱風，會帶來強烈的風和大量的降雨</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>強烈</t>
+          <t>強烈：颱風是一種強烈旋轉的低氣壓系統，中心氣壓非常低</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>停留</t>
+          <t>停留：梅雨是因為冷暖氣團在同一地區交會，形成停留不太移動的滯留鋒面所造成</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>冬季</t>
+          <t>冬季：東北季風從較冷的地區吹來，通常會讓臺灣冬天感覺比較寒冷乾燥</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>季節</t>
+          <t>季節：颱風大多發生在海洋水溫較高的夏季和秋季</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>冷乾</t>
+          <t>冷乾：冬天大陸冷氣團南下,從東北方吹向臺灣,帶來乾冷的東北季風</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>低壓</t>
+          <t>低壓：颱風是熱帶海面上發展出的強烈低氣壓系統,夏秋常侵襲臺灣帶來強風豪雨</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>夏季</t>
+          <t>夏季：西南季風從溫暖的海洋吹來，帶著大量水氣，使臺灣夏天既炎熱又潮濕</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>低壓中心</t>
+          <t>低壓中心：颱風最中央風雨反而平靜的區域稱為颱風眼，是整個低壓系統的中心</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>滯留</t>
+          <t>滯留：滯留鋒面在同一地區停留很久、不太往前移動，導致該地區連續多天下雨</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>冷空氣</t>
+          <t>冷空氣：冬季寒流是強烈的東北季風把來自高緯度的冷空氣一路帶到臺灣造成的</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>水源</t>
+          <t>水源：颱風雖然常造成災害，但也帶來大量降雨，能有效補充水庫和地下水資源</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>季風</t>
+          <t>季風：臺灣的氣候會隨著季節轉換吹不同方向的風，屬於季風氣候區</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>海溫</t>
+          <t>海溫：颱風是靠吸收溫暖海面蒸發的大量水氣所釋放的熱能來維持與增強</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>轉向</t>
+          <t>轉向：季風會隨著季節不同而改變吹拂的方向，冬夏風向明顯不同</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>熱濕</t>
+          <t>熱濕：夏天風向轉為由西南方吹來,經過廣大海面帶來大量水氣,形成溫暖潮濕的西南季風</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>強烈</t>
+          <t>強烈：颱風中心氣壓遠低於周圍,是一種發展強烈的熱帶低氣壓系統</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>季風</t>
+          <t>季風：臺灣冬天吹來自大陸的東北季風，性質寒冷乾燥；夏天則吹來自海洋的西南季風，性質炎熱潮濕，方向和性質都不同</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>低壓</t>
+          <t>低壓：颱風是強烈旋轉的低氣壓系統，旋轉的氣流形成強風，同時挾帶著從海面吸收的大量水氣，凝結後降下豪雨</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>冬東北季風冷乾夏西南季風熱濕</t>
+          <t>冬季吹東北季風,乾冷;夏季吹西南季風,溫暖潮濕</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>利弊</t>
+          <t>利弊：梅雨帶來的降雨能補充臺灣重要的水資源，但如果下太久也容易造成淹水等災害，是一體兩面</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>防災</t>
+          <t>防災：颱風來臨前要注意氣象預警訊息、提前準備民生物資，並遠離山坡地、海邊等容易發生危險的地區</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>雙面</t>
+          <t>雙面：颱風強風豪雨可能造成淹水、土石流等災害，但同時也為水庫和農業帶來急需的大量降雨，補充水資源</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>寒流</t>
+          <t>寒流：當東北季風特別強烈時，會把高緯度的冷空氣大量往南帶到臺灣，使氣溫在短時間內大幅下降形成寒流</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>地形雨</t>
+          <t>地形雨：潮濕的風吹向山脈時，在迎風的一側被迫抬升冷卻形成豐富降雨，翻過山後的背風面則變得比較乾燥</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>冬東北季風冷乾夏西南季風熱濕</t>
+          <t>冬季吹東北季風,乾冷;夏季吹西南季風,溫暖潮濕</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：臺灣隨著季節輪替吹拂不同方向的季風，冬季冷乾、夏季熱濕，季風的轉換就塑造出臺灣四季分明的天氣型態</t>
         </is>
       </c>
     </row>
@@ -1830,27 +1830,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>說明臺灣冬夏季風的差異？</t>
+          <t>比較臺灣冬季與夏季季風方向和性質的差異？</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>季風轉換帶來乾濕冷熱變化</t>
+          <t>致災同時補充水庫</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>冬東北季風冷乾、夏西南季風熱濕</t>
+          <t>強東北季風冷空氣南下氣溫驟降</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>強東北季風冷空氣南下氣溫驟降</t>
+          <t>強烈低壓旋轉挾帶大量水氣</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>冬東北季風冷乾夏西南季風熱濕</t>
+          <t>冬季吹東北季風,乾冷;夏季吹西南季風,溫暖潮濕</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>季風</t>
+          <t>對比：冬季受大陸冷氣團影響吹東北季風,性質乾冷;夏季風向轉為西南季風,經過海面帶來大量水氣,性質溫暖潮濕,兩季風向與性質剛好相反</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>冬東北季風冷乾夏西南季風熱濕</t>
+          <t>冬季吹東北季風,乾冷;夏季吹西南季風,溫暖潮濕</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>雙面</t>
+          <t>雙面：颱風雖然常造成災害,但也帶來大量降雨,是臺灣水庫重要的進水來源之一,對缺水問題有很大幫助</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-3_三種難度測驗卷.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>較冷乾</t>
+          <t>梅雨</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>較熱濕</t>
+          <t>夏秋</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>西南季風</t>
+          <t>東北季風</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>低氣壓</t>
+          <t>梅雨</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>較熱濕</t>
+          <t>季風氣候區</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>西南季風</t>
+          <t>溫暖海洋水氣</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>東北季風</t>
+          <t>季風氣候區</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>溫暖海洋水氣</t>
+          <t>梅雨</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>颱風</t>
+          <t>滯留鋒面</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
